--- a/exports/colleges/3004_miranda-house-new-delhi.xlsx
+++ b/exports/colleges/3004_miranda-house-new-delhi.xlsx
@@ -605,11 +605,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -712,7 +712,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Jan - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Jan - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,17 +846,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10+2 with CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>CUET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Jan - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>B.Ed</t>
+          <t>Bachelor of Elementary Education [B.El.Ed]</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,17 +888,17 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bachelor of Elementary Education [B.El.Ed]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>82,440</t>
+          <t>82440</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Graduation</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Jul 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Graduate Certificate in Science</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,7 +950,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -960,7 +960,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1 Year</t>
+          <t>1 year</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>10+2</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>18 Oct - 10 Nov 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BA {Hons.}</t>
+          <t>Master of Arts [MA]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>BA {Hons.}</t>
+          <t>Master of Arts [MA]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>48,180 - 55,740</t>
+          <t>32,060</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Jul 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.}</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.}</t>
+          <t>Master of Science [M.Sc]</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>55,800 - 60,300</t>
+          <t>32,060 - 32,140</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1099,12 +1099,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>15 May - 04 Jul 2026</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>B.El.Ed</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>B.El.Ed</t>
+          <t>Bachelor of Arts [BA]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>B.El.Ed</t>
+          <t>Bachelor of Arts [BA]</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82,440</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Jan - 30 Jan 2026</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Bachelor of Arts [BA] {Hons.}</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Bachelor of Arts [BA] {Hons.}</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>5,000</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with CUET</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CUET</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Bachelor of Science [B.Sc] {Hons.}</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>Bachelor of Science [B.Sc] {Hons.}</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32,060</t>
+          <t>60,300</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with CUET</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>CUET</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M.Sc</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32,060 - 32,140</t>
+          <t>60,270</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2 Years</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,12 +1342,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with CUET</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>IIT JAM</t>
+          <t>CUET</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>B.Ed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BA {Hons.} Political Science</t>
+          <t>Bachelor of Elementary Education [B.El.Ed]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BA {Hons.} Political Science</t>
+          <t>Bachelor of Elementary Education [B.El.Ed]</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>82,440</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>Graduate Certificate in Science</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BA {Hons.} Economics</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BA {Hons.} Economics</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>1 Year</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1503,17 +1503,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BA {Hons.} English</t>
+          <t>BA {Hons.}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BA {Hons.} English</t>
+          <t>BA {Hons.}</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>48,180 - 55,740</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1560,22 +1560,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BA {Hons.} Geography</t>
+          <t>B.Sc {Hons.}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>BA {Hons.} Geography</t>
+          <t>B.Sc {Hons.}</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55,740</t>
+          <t>55,800 - 60,300</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BA</t>
+          <t>B.El.Ed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BA {Hons.} History</t>
+          <t>B.El.Ed</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>BA {Hons.} History</t>
+          <t>B.El.Ed</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>82,440</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1684,22 +1684,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sociology</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>5,000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Hindi</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>32,060</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Music</t>
+          <t>M.Sc</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>48,180</t>
+          <t>32,060 - 32,140</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 Years</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>IIT JAM</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1870,17 +1870,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>BA {Hons.} Political Science</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>BA {Hons.} Political Science</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1932,17 +1932,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>BA {Hons.} Economics</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Bengali</t>
+          <t>BA {Hons.} Economics</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Zoology</t>
+          <t>BA {Hons.} English</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Zoology</t>
+          <t>BA {Hons.} English</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>60,300</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2056,22 +2056,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Chemistry</t>
+          <t>BA {Hons.} Geography</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Chemistry</t>
+          <t>BA {Hons.} Geography</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>60,300</t>
+          <t>55,740</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2118,22 +2118,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>BA</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Physics</t>
+          <t>BA {Hons.} History</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Physics</t>
+          <t>BA {Hons.} History</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>60,300</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2180,27 +2180,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Mathematics</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Mathematics</t>
+          <t>Sociology</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55,800</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2242,27 +2242,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Botany</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.} Botany</t>
+          <t>Hindi</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>60,300</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2304,27 +2304,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>B.Sc Life Sciences</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>B.Sc Life Sciences</t>
+          <t>Music</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>60,270</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2366,27 +2366,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>B.Sc Physical Sciences</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>B.Sc Physical Sciences</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>58,770</t>
+          <t>48,180</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2428,25 +2428,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B.El.Ed</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>B.El.Ed (General)</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>Bengali</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>82,440</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>48,180</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2486,25 +2490,29 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Certification (General)</t>
+          <t>B.Sc {Hons.} Zoology</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>B.Sc {Hons.} Zoology</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>5,000</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>60,300</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2544,25 +2552,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MA (General)</t>
+          <t>B.Sc {Hons.} Chemistry</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>General</t>
+          <t>B.Sc {Hons.} Chemistry</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32,060</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>60,300</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -2602,51 +2614,535 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>B.Sc {Hons.} Physics</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>B.Sc {Hons.} Physics</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>60,300</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>B.Sc {Hons.} Mathematics</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>B.Sc {Hons.} Mathematics</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>55,800</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>B.Sc {Hons.} Botany</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>B.Sc {Hons.} Botany</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>60,300</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>B.Sc Life Sciences</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>B.Sc Life Sciences</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>60,270</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>B.Sc</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>B.Sc Physical Sciences</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>B.Sc Physical Sciences</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>58,770</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>3 Years</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>B.El.Ed</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>B.El.Ed (General)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>82,440</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Certification</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Certification (General)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>5,000</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MA (General)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>General</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>32,060</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Full Time</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>UG</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>M.Sc</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>M.Sc (General)</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>General</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>32,060 - 32,140</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>Full Time</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Not Specified</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
